--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260910.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>16,261,073</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,261,073</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
